--- a/output/pdf_financials_xlsx/GRSL.xlsx
+++ b/output/pdf_financials_xlsx/GRSL.xlsx
@@ -469,15 +469,11 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -486,15 +482,11 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -503,15 +495,11 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -520,15 +508,11 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.671735</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.7898230000000001</v>
       </c>
     </row>
     <row r="8">
@@ -537,15 +521,11 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -554,15 +534,11 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -571,15 +547,11 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>-3.679367</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>-7.737549</v>
       </c>
     </row>
     <row r="11">
@@ -588,15 +560,11 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>3.679367</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>7.737549</v>
       </c>
     </row>
     <row r="12">
@@ -605,15 +573,11 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -622,15 +586,11 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -639,15 +599,11 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -656,15 +612,11 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0.057563</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>0.074612</v>
       </c>
     </row>
     <row r="16">
@@ -673,15 +625,11 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-3.69413</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-8.743671000000001</v>
       </c>
     </row>
     <row r="17">
@@ -690,15 +638,11 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -741,15 +685,11 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-3.69413</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-8.743671000000001</v>
       </c>
     </row>
     <row r="21">
@@ -758,15 +698,11 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -775,15 +711,11 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -856,15 +788,11 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-3.69413</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-8.743671000000001</v>
       </c>
     </row>
     <row r="28">
@@ -873,15 +801,11 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -890,15 +814,11 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-3.69413</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-8.743671000000001</v>
       </c>
     </row>
     <row r="30">
@@ -924,15 +844,11 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -965,15 +881,11 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -982,15 +894,11 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -999,15 +907,11 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1016,15 +920,11 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1033,15 +933,11 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1050,15 +946,11 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1067,15 +959,11 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1097,15 +985,11 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1114,15 +998,11 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1131,15 +1011,11 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1148,15 +1024,11 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1165,15 +1037,11 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1182,15 +1050,11 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1199,15 +1063,11 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>2.087752</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>4.991597</v>
       </c>
     </row>
     <row r="49">
@@ -1216,15 +1076,11 @@
           <t xml:space="preserve">  Total Current Assets</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="3" t="n">
+        <v>2.105978</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>5.030156</v>
       </c>
     </row>
     <row r="50">
@@ -1233,15 +1089,11 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1250,15 +1102,11 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1267,15 +1115,11 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1284,15 +1128,11 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1301,15 +1141,11 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1335,15 +1171,11 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1352,15 +1184,11 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1369,15 +1197,11 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>0.927611</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>3.70668</v>
       </c>
     </row>
     <row r="59">
@@ -1386,15 +1210,11 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1403,15 +1223,11 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1420,15 +1236,11 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0.630305</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>2.107175</v>
       </c>
     </row>
     <row r="62">
@@ -1437,15 +1249,11 @@
           <t xml:space="preserve">  Total Long-Term Assets</t>
         </is>
       </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="3" t="n">
+        <v>1.557916</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>5.813855</v>
       </c>
     </row>
     <row r="63">
@@ -1454,15 +1262,11 @@
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="B63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B63" s="3" t="n">
+        <v>3.663894</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>10.844011</v>
       </c>
     </row>
     <row r="64">
@@ -1471,15 +1275,11 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1488,15 +1288,11 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1505,15 +1301,11 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1522,15 +1314,11 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -1552,15 +1340,11 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -1569,15 +1353,11 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1586,15 +1366,11 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -1603,15 +1379,11 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1620,15 +1392,11 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1637,15 +1405,11 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -1654,15 +1418,11 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -1688,15 +1448,11 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -1705,15 +1461,11 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -1722,15 +1474,11 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -1756,15 +1504,11 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -1773,15 +1517,11 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -1790,15 +1530,11 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -1807,15 +1543,11 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -1824,15 +1556,11 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -1871,15 +1599,11 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>13.207803</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>27.300384</v>
       </c>
     </row>
     <row r="89">
@@ -1888,15 +1612,11 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -1918,15 +1638,11 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -1935,15 +1651,11 @@
           <t xml:space="preserve">  Additional Paid-In Capital</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -1952,15 +1664,11 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -1969,15 +1677,11 @@
           <t xml:space="preserve">  Total Stockholders Equity</t>
         </is>
       </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="3" t="n">
+        <v>3.291168</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>9.667253000000001</v>
       </c>
     </row>
     <row r="95">
@@ -1986,15 +1690,11 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2003,15 +1703,11 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>3.291168</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>9.667253000000001</v>
       </c>
     </row>
     <row r="97">
@@ -2020,15 +1716,11 @@
           <t>Equity-to-Asset</t>
         </is>
       </c>
-      <c r="B97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B97" s="3" t="n">
+        <v>0.898270528568785</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>0.8914831421694427</v>
       </c>
     </row>
     <row r="98">
@@ -2044,15 +1736,11 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-3.69413</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>-8.743671000000001</v>
       </c>
     </row>
     <row r="100">
@@ -2061,15 +1749,11 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2078,15 +1762,11 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -2095,15 +1775,11 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2112,15 +1788,11 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -2130,10 +1802,10 @@
         </is>
       </c>
       <c r="B104" s="3" t="n">
-        <v>0.306267</v>
+        <v>0.327267</v>
       </c>
       <c r="C104" s="3" t="n">
-        <v>0.6696800000000001</v>
+        <v>0.825672</v>
       </c>
     </row>
     <row r="105">
@@ -2142,15 +1814,11 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2159,15 +1827,11 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.327267</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>0.825672</v>
       </c>
     </row>
     <row r="107">
@@ -2177,7 +1841,7 @@
         </is>
       </c>
       <c r="B107" s="3" t="n">
-        <v>0.325749</v>
+        <v>1.700573</v>
       </c>
       <c r="C107" s="3" t="n">
         <v>1.049075</v>
@@ -2189,15 +1853,11 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2206,15 +1866,11 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2223,15 +1879,11 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2240,15 +1892,11 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -2257,15 +1905,11 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2274,15 +1918,11 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2291,15 +1931,11 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2308,15 +1944,11 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2325,15 +1957,11 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2342,15 +1970,11 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2359,15 +1983,11 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>-0.047711</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0.540111</v>
       </c>
     </row>
     <row r="119">
@@ -2389,15 +2009,11 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2406,15 +2022,11 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2423,15 +2035,11 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2440,15 +2048,11 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -2457,15 +2061,11 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -2474,15 +2074,11 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -2491,15 +2087,11 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -2525,15 +2117,11 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>-0.306304</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>-0.886344</v>
       </c>
     </row>
     <row r="129">
@@ -2568,15 +2156,11 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -2585,15 +2169,11 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>0.765382</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>2.844068</v>
       </c>
     </row>
     <row r="133">
@@ -2615,15 +2195,11 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -2632,15 +2208,11 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-3.152115</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>-6.554278</v>
       </c>
     </row>
   </sheetData>
@@ -2654,7 +2226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2795,7 +2367,11 @@
           <t>Current total</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CurrentAssets</t>
+        </is>
+      </c>
       <c r="E5" s="5" t="n">
         <v>2.105978</v>
       </c>
@@ -2871,7 +2447,11 @@
           <t>Exploration and evaluation assets (Note 7)</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E8" s="5" t="n">
         <v>0.927611</v>
       </c>
@@ -2911,20 +2491,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Current</t>
+          <t>Current liabilities</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>$ 10,</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>Accounts payable and accrued liabilities (Note 9 and 10) $</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E10" s="5" t="n">
-        <v>3.663894</v>
+        <v>0.372726</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.844011</v>
+        <v>0.961297</v>
       </c>
     </row>
     <row r="11">
@@ -2935,24 +2519,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Current liabilities</t>
+          <t>Non-current liabilities</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities (Note 9 and 10) $</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>PayablesAndAccruedExpenses</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>0.372726</v>
+          <t>Reclamation provision (Note 11)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.961297</v>
+        <v>0.215461</v>
       </c>
     </row>
     <row r="12">
@@ -2968,17 +2550,19 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Reclamation provision (Note 11)</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TotalLiabilities</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.372726</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.215461</v>
+        <v>1.176758</v>
       </c>
     </row>
     <row r="13">
@@ -2989,24 +2573,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Non-current liabilities</t>
+          <t>Shareholders’ equity</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Total liabilities</t>
+          <t>Share capital (Note 12)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>TotalLiabilities</t>
+          <t>CapitalStock</t>
         </is>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.372726</v>
+        <v>13.207803</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>1.176758</v>
+        <v>27.300384</v>
       </c>
     </row>
     <row r="14">
@@ -3022,19 +2606,15 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Share capital (Note 12)</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>CapitalStock</t>
-        </is>
-      </c>
+          <t>Share compensation reserve (Note 12)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" s="5" t="n">
-        <v>13.207803</v>
+        <v>1.461881</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>27.300384</v>
+        <v>2.489056</v>
       </c>
     </row>
     <row r="15">
@@ -3050,15 +2630,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Share compensation reserve (Note 12)</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Deficit</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>RetainedEarnings</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="n">
-        <v>1.461881</v>
+        <v>-11.378516</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>2.489056</v>
+        <v>-20.122187</v>
       </c>
     </row>
     <row r="16">
@@ -3074,67 +2658,75 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Deficit</t>
+          <t>Shareholders’ equity total</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>RetainedEarnings</t>
+          <t>StockholdersEquity</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
-        <v>-11.378516</v>
+        <v>3.291168</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>-20.122187</v>
+        <v>9.667253000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Shareholders’ equity</t>
+          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Shareholders’ equity total</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Loss for the year $</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="n">
-        <v>3.291168</v>
+        <v>-3.69413</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>9.667253000000001</v>
+        <v>-8.743671000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Shareholders’ equity</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>$</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Amortization (Note 5)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E18" s="5" t="n">
-        <v>3.663894</v>
+        <v>0.005615</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>10.844011</v>
+        <v>0.088796</v>
       </c>
     </row>
     <row r="19">
@@ -3145,20 +2737,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM OPERATING ACTIVITIES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Loss for the year $</t>
+          <t>Accretion expense on restoration obligation (Note 11)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
-      <c r="E19" s="5" t="n">
-        <v>-3.69413</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F19" s="5" t="n">
-        <v>-8.743671000000001</v>
+        <v>0.00477</v>
       </c>
     </row>
     <row r="20">
@@ -3174,19 +2768,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Amortization (Note 5)</t>
+          <t>Loss on settlement of accounts payable (Note 12)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Amortization</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.005615</v>
+        <v>0.021</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.088796</v>
+        <v>0.155992</v>
       </c>
     </row>
     <row r="21">
@@ -3202,17 +2796,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Accretion expense on restoration obligation (Note 11)</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share-based compensation (Note 10 and 12)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0.325749</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.00477</v>
+        <v>1.049075</v>
       </c>
     </row>
     <row r="22">
@@ -3228,15 +2824,21 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Loss on settlement of accounts payable (Note 12)</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" s="5" t="n">
-        <v>0.021</v>
+          <t>Impairment on exploration and evaluation assets (Note 7)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.155992</v>
+        <v>0.560268</v>
       </c>
     </row>
     <row r="23">
@@ -3252,19 +2854,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 10 and 12)</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="n">
-        <v>0.325749</v>
+          <t>Impairment on value added tax</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F23" s="5" t="n">
-        <v>1.049075</v>
+        <v>0.302596</v>
       </c>
     </row>
     <row r="24">
@@ -3275,22 +2875,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Impairment on exploration and evaluation assets (Note 7)</t>
+          <t>Decrease in receivables</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E24" s="5" t="n">
+        <v>0.00047</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.560268</v>
+        <v>-0.009238</v>
       </c>
     </row>
     <row r="25">
@@ -3301,22 +2899,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Items not affecting cash</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Impairment on value added tax</t>
+          <t>Increase in value added tax</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E25" s="5" t="n">
+        <v>-0.149256</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0.302596</v>
+        <v>-0.572769</v>
       </c>
     </row>
     <row r="26">
@@ -3332,15 +2928,15 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Decrease in receivables</t>
+          <t>Increase (decrease) in prepaids</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" s="5" t="n">
-        <v>0.00047</v>
+        <v>0.03217</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>-0.009238</v>
+        <v>-0.059777</v>
       </c>
     </row>
     <row r="27">
@@ -3356,15 +2952,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Increase in value added tax</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
+          <t>Increase in accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E27" s="5" t="n">
-        <v>-0.149256</v>
+        <v>0.306267</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>-0.572769</v>
+        <v>0.6696800000000001</v>
       </c>
     </row>
     <row r="28">
@@ -3380,15 +2980,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Increase (decrease) in prepaids</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
+          <t>Net cash used in operating activities</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E28" s="5" t="n">
-        <v>0.03217</v>
+        <v>-3.152115</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>-0.059777</v>
+        <v>-6.554278</v>
       </c>
     </row>
     <row r="29">
@@ -3399,24 +3003,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Increase in accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>0.306267</v>
+          <t>Cash acquired from Plomosas acquisition (Note 8)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F29" s="5" t="n">
-        <v>0.6696800000000001</v>
+        <v>0.002379</v>
       </c>
     </row>
     <row r="30">
@@ -3427,24 +3029,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>-3.152115</v>
+          <t>Acquisition of Plomosas Property (Note 7)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F30" s="5" t="n">
-        <v>-6.554278</v>
+        <v>-0.25716</v>
       </c>
     </row>
     <row r="31">
@@ -3460,17 +3060,15 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cash acquired from Plomosas acquisition (Note 8)</t>
+          <t>Deferred acquisition costs</t>
         </is>
       </c>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E31" s="5" t="n">
+        <v>-0.05</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0.002379</v>
+        <v>-0.10886</v>
       </c>
     </row>
     <row r="32">
@@ -3486,17 +3084,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Acquisition of Plomosas Property (Note 7)</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Exploration and evaluation assets</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>-0.047711</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>-0.25716</v>
+        <v>-0.020157</v>
       </c>
     </row>
     <row r="33">
@@ -3512,15 +3112,15 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Deferred acquisition costs</t>
+          <t>Equipment</t>
         </is>
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" s="5" t="n">
-        <v>-0.05</v>
+        <v>-0.054738</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>-0.10886</v>
+        <v>-0.797966</v>
       </c>
     </row>
     <row r="34">
@@ -3536,15 +3136,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Exploration and evaluation assets</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>Net cash used in investing activities</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="n">
-        <v>-0.047711</v>
+        <v>-0.152449</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>-0.020157</v>
+        <v>-1.181764</v>
       </c>
     </row>
     <row r="35">
@@ -3555,20 +3159,24 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Equipment</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>Proceeds from the issuance of shares</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E35" s="5" t="n">
-        <v>-0.054738</v>
+        <v>4.37625</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>-0.797966</v>
+        <v>11.466454</v>
       </c>
     </row>
     <row r="36">
@@ -3579,24 +3187,24 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM INVESTING ACTIVITIES</t>
+          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Net cash used in investing activities</t>
+          <t>Share issue costs</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
+          <t>NetOtherFinancingCharges</t>
         </is>
       </c>
       <c r="E36" s="5" t="n">
-        <v>-0.152449</v>
+        <v>-0.306304</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>-1.181764</v>
+        <v>-0.886344</v>
       </c>
     </row>
     <row r="37">
@@ -3612,19 +3220,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Proceeds from the issuance of shares</t>
+          <t>Net cash provided by financing activities</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>CommonStockIssuance</t>
+          <t>FinancingCashFlow</t>
         </is>
       </c>
       <c r="E37" s="5" t="n">
-        <v>4.37625</v>
+        <v>4.069946</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>11.466454</v>
+        <v>10.58011</v>
       </c>
     </row>
     <row r="38">
@@ -3640,15 +3248,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Share issue costs</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>Change in cash during the year</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
-        <v>-0.306304</v>
+        <v>0.765382</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>-0.886344</v>
+        <v>2.844068</v>
       </c>
     </row>
     <row r="39">
@@ -3664,19 +3276,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
+          <t>Cash, beginning of year</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>4.069946</v>
+        <v>1.284128</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>10.58011</v>
+        <v>2.04951</v>
       </c>
     </row>
     <row r="40">
@@ -3692,15 +3304,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Change in cash during the year</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
+          <t>Cash, end of year $</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E40" s="5" t="n">
-        <v>0.765382</v>
+        <v>2.04951</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>2.844068</v>
+        <v>4.893578</v>
       </c>
     </row>
     <row r="41">
@@ -3711,24 +3327,20 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>shares Amount reserve Deficit Total</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cash, beginning of year</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Balance, December 31, 2018 41,005,572 $ 8,953,345 $ 1,011,772 $</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" s="5" t="n">
-        <v>1.284128</v>
+        <v>2.280731</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>2.04951</v>
+        <v>-7.684386</v>
       </c>
     </row>
     <row r="42">
@@ -3739,24 +3351,22 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CASH FLOWS FROM FINANCING ACTIVITIES</t>
+          <t>Shares issued for cash</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cash, end of year $</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Private placement 26,010,000 4,376,250 -</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" s="5" t="n">
-        <v>2.04951</v>
-      </c>
-      <c r="F42" s="5" t="n">
-        <v>4.893578</v>
+        <v>4.37625</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -3767,20 +3377,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>shares Amount reserve Deficit Total</t>
+          <t>Shares issued for cash</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2018 41,005,572 $ 8,953,345 $ 1,011,772 $</t>
+          <t>Share issue costs - (306,304) -</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" s="5" t="n">
-        <v>2.280731</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>-7.684386</v>
+        <v>-0.306304</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="44">
@@ -3791,17 +3403,19 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Shares issued for cash</t>
+          <t>Shares issued for non-cash</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Private placement 26,010,000 4,376,250 -</t>
+          <t>Finder’s fee – warrants issued - (124,360) 124,360</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" s="5" t="n">
-        <v>4.37625</v>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3817,17 +3431,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Shares issued for cash</t>
+          <t>Shares issued for non-cash</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Share issue costs - (306,304) -</t>
+          <t>Debt settlement 1,683,819 308,872 -</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
       <c r="E45" s="5" t="n">
-        <v>-0.306304</v>
+        <v>0.308872</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3848,14 +3462,16 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Finder’s fee – warrants issued - (124,360) 124,360</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Share-based compensation - - 325,749</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>0.325749</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3876,17 +3492,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Debt settlement 1,683,819 308,872 -</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>Loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E47" s="5" t="n">
-        <v>0.308872</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3.69413</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>-3.69413</v>
       </c>
     </row>
     <row r="48">
@@ -3902,21 +3520,15 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 325,749</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Balance, December 31, 2019 68,699,391 $ 13,207,803 $ 1,461,881 $</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" s="5" t="n">
-        <v>0.325749</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.291168</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>-11.378516</v>
       </c>
     </row>
     <row r="49">
@@ -3927,20 +3539,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Shares issued for non-cash</t>
+          <t>Shares issued for cash</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Loss for the year - - -</t>
+          <t>Private placement 33,900,000 9,153,000 -</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" s="5" t="n">
-        <v>-3.69413</v>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>-3.69413</v>
+        <v>9.153</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -3951,20 +3565,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Shares issued for non-cash</t>
+          <t>Shares issued for cash</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2019 68,699,391 $ 13,207,803 $ 1,461,881 $</t>
+          <t>Exercise of warrants 7,148,149 2,081,730 -</t>
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" s="5" t="n">
-        <v>3.291168</v>
-      </c>
-      <c r="F50" s="5" t="n">
-        <v>-11.378516</v>
+        <v>2.08173</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="51">
@@ -3980,12 +3596,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Private placement 33,900,000 9,153,000 -</t>
+          <t>Exercise of options 925,000 231,725 -</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" s="5" t="n">
-        <v>9.153</v>
+        <v>0.231725</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -4006,12 +3622,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Exercise of warrants 7,148,149 2,081,730 -</t>
+          <t>Share issue costs - (886,344) -</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" s="5" t="n">
-        <v>2.08173</v>
+        <v>-0.886344</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -4027,17 +3643,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Shares issued for cash</t>
+          <t>Shares issued for non-cash</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Exercise of options 925,000 231,725 -</t>
+          <t>Reclassification of reserves on exercise - 221,606 (221,606)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" s="5" t="n">
-        <v>0.231725</v>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -4053,17 +3671,19 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Shares issued for cash</t>
+          <t>of warrants</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Share issue costs - (886,344) -</t>
+          <t>Reclassification of reserves on exercise - 159,552 (159,552)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" s="5" t="n">
-        <v>-0.886344</v>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -4079,12 +3699,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Shares issued for non-cash</t>
+          <t>of options</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Reclassification of reserves on exercise - 221,606 (221,606)</t>
+          <t>Finder’s fees – warrants issued - (359,258) 359,258</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
@@ -4107,19 +3727,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>of warrants</t>
+          <t>of options</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Reclassification of reserves on exercise - 159,552 (159,552)</t>
+          <t>Property acquisition 17,847,500 3,131,575 -</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E56" s="5" t="n">
+        <v>3.131575</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -4140,14 +3758,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Finder’s fees – warrants issued - (359,258) 359,258</t>
+          <t>Debt settlement 427,375 358,995 -</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E57" s="5" t="n">
+        <v>0.358995</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4168,12 +3784,16 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Property acquisition 17,847,500 3,131,575 -</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
+          <t>Share-based compensation - - 1,049,075</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E58" s="5" t="n">
-        <v>3.131575</v>
+        <v>1.049075</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -4194,17 +3814,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Debt settlement 427,375 358,995 -</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>Loss for the year - - -</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E59" s="5" t="n">
-        <v>0.358995</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-8.743671000000001</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>-8.743671000000001</v>
       </c>
     </row>
     <row r="60">
@@ -4220,69 +3842,67 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Share-based compensation - - 1,049,075</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
+          <t>Balance, December 31, 2020 128,947,415 $ 27,300,384 $ 2,489,056 $</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" s="5" t="n">
-        <v>1.049075</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9.667253000000001</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>-20.122187</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>of options</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Loss for the year - - -</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr"/>
+          <t>Amortization (Note 5) $</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
       <c r="E61" s="5" t="n">
-        <v>-8.743671000000001</v>
+        <v>0.005615</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>-8.743671000000001</v>
+        <v>0.088796</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>income_statement</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>of options</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Balance, December 31, 2020 128,947,415 $ 27,300,384 $ 2,489,056 $</t>
+          <t>Consulting (Note 10)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" s="5" t="n">
-        <v>9.667253000000001</v>
+        <v>0.430516</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>-20.122187</v>
+        <v>0.768385</v>
       </c>
     </row>
     <row r="63">
@@ -4298,19 +3918,15 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Amortization (Note 5) $</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Amortization</t>
-        </is>
-      </c>
+          <t>Exploration expenditures (Note 8 and 10)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" s="5" t="n">
-        <v>0.005615</v>
+        <v>1.797846</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>0.088796</v>
+        <v>4.35509</v>
       </c>
     </row>
     <row r="64">
@@ -4326,15 +3942,19 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Consulting (Note 10)</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E64" s="5" t="n">
-        <v>0.430516</v>
+        <v>0.051326</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>0.768385</v>
+        <v>0.057108</v>
       </c>
     </row>
     <row r="65">
@@ -4350,15 +3970,19 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Exploration expenditures (Note 8 and 10)</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>Investor relations</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E65" s="5" t="n">
-        <v>1.797846</v>
+        <v>0.554108</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>4.35509</v>
+        <v>0.73267</v>
       </c>
     </row>
     <row r="66">
@@ -4374,15 +3998,15 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Office</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" s="5" t="n">
-        <v>0.051326</v>
+        <v>0.159424</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>0.057108</v>
+        <v>0.244711</v>
       </c>
     </row>
     <row r="67">
@@ -4398,15 +4022,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Investor relations</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
+          <t>Professional fees (Note 10)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E67" s="5" t="n">
-        <v>0.554108</v>
+        <v>0.188636</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>0.73267</v>
+        <v>0.251822</v>
       </c>
     </row>
     <row r="68">
@@ -4422,15 +4050,17 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Property investigation</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" s="5" t="n">
-        <v>0.159424</v>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F68" s="5" t="n">
-        <v>0.244711</v>
+        <v>0.043568</v>
       </c>
     </row>
     <row r="69">
@@ -4446,19 +4076,15 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Professional fees (Note 10)</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Share-based compensation (Note 10 and 12)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" s="5" t="n">
-        <v>0.188636</v>
+        <v>0.325749</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>0.251822</v>
+        <v>1.049075</v>
       </c>
     </row>
     <row r="70">
@@ -4474,17 +4100,15 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Property investigation</t>
+          <t>Transfer agent</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E70" s="5" t="n">
+        <v>0.04852</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>0.043568</v>
+        <v>0.089171</v>
       </c>
     </row>
     <row r="71">
@@ -4500,15 +4124,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Share-based compensation (Note 10 and 12)</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E71" s="5" t="n">
-        <v>0.325749</v>
+        <v>0.117627</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>1.049075</v>
+        <v>0.057153</v>
       </c>
     </row>
     <row r="72">
@@ -4524,15 +4152,19 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Transfer agent</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>EXPENSES total</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E72" s="5" t="n">
-        <v>0.04852</v>
+        <v>-3.679367</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>0.089171</v>
+        <v>-7.737549</v>
       </c>
     </row>
     <row r="73">
@@ -4548,15 +4180,17 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Travel</t>
+          <t>Accretion expense on restoration obligation (Note 11)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
-      <c r="E73" s="5" t="n">
-        <v>0.117627</v>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F73" s="5" t="n">
-        <v>0.057153</v>
+        <v>-0.00477</v>
       </c>
     </row>
     <row r="74">
@@ -4572,15 +4206,17 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>EXPENSES total</t>
+          <t>Impairment on exploration and evaluation assets (Note 7)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" s="5" t="n">
-        <v>-3.679367</v>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F74" s="5" t="n">
-        <v>-7.737549</v>
+        <v>-0.560268</v>
       </c>
     </row>
     <row r="75">
@@ -4596,7 +4232,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Accretion expense on restoration obligation (Note 11)</t>
+          <t>Impairment on value added tax</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
@@ -4606,7 +4242,7 @@
         </is>
       </c>
       <c r="F75" s="5" t="n">
-        <v>-0.00477</v>
+        <v>-0.302596</v>
       </c>
     </row>
     <row r="76">
@@ -4622,17 +4258,15 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Impairment on exploration and evaluation assets (Note 7)</t>
+          <t>Loss on settlement of accounts payable (Note 12)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E76" s="5" t="n">
+        <v>-0.021</v>
       </c>
       <c r="F76" s="5" t="n">
-        <v>-0.560268</v>
+        <v>-0.155992</v>
       </c>
     </row>
     <row r="77">
@@ -4648,17 +4282,19 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Impairment on value added tax</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>0.006237</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>-0.302596</v>
+        <v>0.017504</v>
       </c>
     </row>
     <row r="78">
@@ -4674,15 +4310,19 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Loss on settlement of accounts payable (Note 12)</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>Loss and comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E78" s="5" t="n">
-        <v>-0.021</v>
+        <v>-3.69413</v>
       </c>
       <c r="F78" s="5" t="n">
-        <v>-0.155992</v>
+        <v>-8.743671000000001</v>
       </c>
     </row>
     <row r="79">
@@ -4693,71 +4333,19 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Weighted average number of common shares outstanding</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Other income</t>
+          <t>-Basic and diluted</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" s="5" t="n">
-        <v>0.006237</v>
+        <v>49.58167</v>
       </c>
       <c r="F79" s="5" t="n">
-        <v>0.017504</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Loss and comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E80" s="5" t="n">
-        <v>-3.69413</v>
-      </c>
-      <c r="F80" s="5" t="n">
-        <v>-8.743671000000001</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Weighted average number of common shares outstanding</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>-Basic and diluted</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" s="5" t="n">
-        <v>49.58167</v>
-      </c>
-      <c r="F81" s="5" t="n">
         <v>102.853476</v>
       </c>
     </row>

--- a/output/pdf_financials_xlsx/GRSL.xlsx
+++ b/output/pdf_financials_xlsx/GRSL.xlsx
@@ -431,6 +431,11 @@
   </sheetPr>
   <dimension ref="A1:C135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/GRSL.xlsx
+++ b/output/pdf_financials_xlsx/GRSL.xlsx
@@ -540,10 +540,10 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0</v>
+        <v>0.63846</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0</v>
+        <v>1.102267</v>
       </c>
     </row>
     <row r="10">
@@ -553,10 +553,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>-3.679367</v>
+        <v>3.679367</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>-7.737549</v>
+        <v>7.737549</v>
       </c>
     </row>
     <row r="11">
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>3.679367</v>
+        <v>-3.679367</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>7.737549</v>
+        <v>-7.737549</v>
       </c>
     </row>
     <row r="12">
@@ -592,10 +592,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -644,10 +644,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>0</v>
+        <v>0.064692</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>0</v>
+        <v>1.166637</v>
       </c>
     </row>
     <row r="54">
@@ -2400,7 +2400,11 @@
           <t>Equipment (Note 5)</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E6" s="5" t="n">
         <v>0.064692</v>
       </c>
@@ -3902,7 +3906,11 @@
           <t>Consulting (Note 10)</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E62" s="5" t="n">
         <v>0.430516</v>
       </c>
@@ -4006,7 +4014,11 @@
           <t>Office</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E66" s="5" t="n">
         <v>0.159424</v>
       </c>
@@ -4108,7 +4120,11 @@
           <t>Transfer agent</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E70" s="5" t="n">
         <v>0.04852</v>
       </c>
@@ -4166,10 +4182,10 @@
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>-3.679367</v>
+        <v>3.679367</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>-7.737549</v>
+        <v>7.737549</v>
       </c>
     </row>
     <row r="73">

--- a/output/pdf_financials_xlsx/GRSL.xlsx
+++ b/output/pdf_financials_xlsx/GRSL.xlsx
@@ -887,10 +887,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.04951</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>4.893578</v>
       </c>
     </row>
     <row r="35">
@@ -913,10 +913,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.04951</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>4.893578</v>
       </c>
     </row>
     <row r="37">
@@ -1069,10 +1069,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.087752</v>
+        <v>0.038242</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>4.991597</v>
+        <v>0.098019</v>
       </c>
     </row>
     <row r="49">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">

--- a/output/pdf_financials_xlsx/GRSL.xlsx
+++ b/output/pdf_financials_xlsx/GRSL.xlsx
@@ -1320,10 +1320,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.032</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="68">
